--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef9390b5f4c6d99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10X Genomics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>10X Genomics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,52 +906,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer (II or Senior) - Backend</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Distro</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4da24314e707fe</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer (II or Senior) - Backend</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Distro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4da24314e707fe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Architect | Cloud Ecosystem</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, SQL Server, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b53178b727cb243</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=06b6b6a5ce025320</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=7c755a205934bcc5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b4c5e318ab3a48</t>
+          <t>https://www.indeed.com/viewjob?jk=b6837d4a932a91bd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b6b6a5ce025320</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c755a205934bcc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a100ab935210c730</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6837d4a932a91bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a20313f7d2a7a9dc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=cd91e562ca9970a9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a100ab935210c730</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20313f7d2a7a9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd91e562ca9970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Sr IT Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr IT Analyst</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=319a55305b9ec532</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=121388def99607e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=799c882a39511da7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java Test Engineer (JUnit, TestNG)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121388def99607e8</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Java Test Engineer (JUnit, TestNG)</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799c882a39511da7</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
@@ -2638,25 +2638,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Developer - Information Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0157074cd30169</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>FINBOA INC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, ETL, CI/CD, Azure DevOps, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=a06d010c371b71c3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=58f4c832c2636335</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=acd89e80e5b6a4a9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=8910d6b03203638d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f4c832c2636335</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4578787be0b9f2</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd89e80e5b6a4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3754942a69259a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8910d6b03203638d</t>
+          <t>https://www.indeed.com/viewjob?jk=fad63a2167a49611</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4578787be0b9f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a16a5489cd0a6c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3754942a69259a</t>
+          <t>https://www.indeed.com/viewjob?jk=64c532176073449a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad63a2167a49611</t>
+          <t>https://www.indeed.com/viewjob?jk=e73e5c1c7670615d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a16a5489cd0a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c16263636cd82ac</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c532176073449a</t>
+          <t>https://www.indeed.com/viewjob?jk=03dc0f27dd5385c5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73e5c1c7670615d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd30fe2b092e173b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c16263636cd82ac</t>
+          <t>https://www.indeed.com/viewjob?jk=924ea1c60bfa48b9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dc0f27dd5385c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac8e729a23523d</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd30fe2b092e173b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3e89e3f671e6cf</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924ea1c60bfa48b9</t>
+          <t>https://www.indeed.com/viewjob?jk=71d64b7ec6bf8924</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac8e729a23523d</t>
+          <t>https://www.indeed.com/viewjob?jk=18d6426f3ca1471f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3e89e3f671e6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=da2abe4a0d0b69f5</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d64b7ec6bf8924</t>
+          <t>https://www.indeed.com/viewjob?jk=c9561276c4b62baa</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d6426f3ca1471f</t>
+          <t>https://www.indeed.com/viewjob?jk=e51238d501b9bd68</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2abe4a0d0b69f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bff725b7fc4f66a1</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9561276c4b62baa</t>
+          <t>https://www.indeed.com/viewjob?jk=022d8a411bdd56e7</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51238d501b9bd68</t>
+          <t>https://www.indeed.com/viewjob?jk=59baa9be4f0b49d3</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff725b7fc4f66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=46aeb3f3ac977809</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d8a411bdd56e7</t>
+          <t>https://www.indeed.com/viewjob?jk=48e679baaf1cf19b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59baa9be4f0b49d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9711cb306753524e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aeb3f3ac977809</t>
+          <t>https://www.indeed.com/viewjob?jk=3a63ff450a71e686</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e679baaf1cf19b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2c60e31be86d72</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9711cb306753524e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcd4041328a571af</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a63ff450a71e686</t>
+          <t>https://www.indeed.com/viewjob?jk=41aad0d287c9996d</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2c60e31be86d72</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2281b12ebdff08</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd4041328a571af</t>
+          <t>https://www.indeed.com/viewjob?jk=51190325066248dc</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aad0d287c9996d</t>
+          <t>https://www.indeed.com/viewjob?jk=10486b06f46c5ed0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2281b12ebdff08</t>
+          <t>https://www.indeed.com/viewjob?jk=66c75d4e4df2f251</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51190325066248dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c341ba6dd703ec6</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4275,111 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10486b06f46c5ed0</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66c75d4e4df2f251</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c341ba6dd703ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8cae7d896e73e8f</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef9390b5f4c6d99</t>
+          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,52 +556,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>10X Genomics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr.Golang Developer with Java/Python – R01564313</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b22e184d9f8ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10X Genomics</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
         </is>
       </c>
     </row>
@@ -928,20 +928,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,94 +986,94 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOC Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Kafka, Kafka Connect, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ec1afd188dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer (II or Senior) - Backend</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Distro</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4da24314e707fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Fulfillment Team</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf2d9f2840f1dd</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b6b6a5ce025320</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Senior Data Engineer - Data &amp; ML Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,24 +1991,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a7142d0678ce23</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
@@ -2078,165 +2078,165 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408b75423e54b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Identity Security Fundamentals Analyst</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec444e19fb1a980</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Trainee</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0f98184675c10</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,119 +2526,119 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb5a89eeb259f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,67 +2648,67 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88986bdf4181f36</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Engineering</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319a55305b9ec532</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI/ML Strategy Consultant</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Hive, Sqoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,89 +2736,89 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab46dd91496e3ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,1827 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Analytics Solution Associate</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Kafka API Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Developer - Information Technology</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>United Airlines</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0157074cd30169</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer III</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Event Streaming Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Database Administrator</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>FINBOA INC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, ETL, CI/CD, Azure DevOps, Git, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a06d010c371b71c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f4c832c2636335</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>WI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acd89e80e5b6a4a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8910d6b03203638d</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4578787be0b9f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>VT, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3754942a69259a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fad63a2167a49611</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a16a5489cd0a6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>NM, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c532176073449a</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e73e5c1c7670615d</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c16263636cd82ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ND, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03dc0f27dd5385c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd30fe2b092e173b</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=924ea1c60bfa48b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>NE, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac8e729a23523d</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3e89e3f671e6cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71d64b7ec6bf8924</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18d6426f3ca1471f</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da2abe4a0d0b69f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>NV, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9561276c4b62baa</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>OK, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51238d501b9bd68</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bff725b7fc4f66a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022d8a411bdd56e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>LA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59baa9be4f0b49d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46aeb3f3ac977809</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>MS, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48e679baaf1cf19b</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9711cb306753524e</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a63ff450a71e686</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2c60e31be86d72</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcd4041328a571af</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41aad0d287c9996d</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2281b12ebdff08</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51190325066248dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10486b06f46c5ed0</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>IA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66c75d4e4df2f251</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c341ba6dd703ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Data Quality Engineer (AWS Data Platform)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, RDS, ETL, ELT, dbt, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8cae7d896e73e8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>CrowdStrike Security Trainee</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a27bacbcbe153698</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,24 +2866,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; ML Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Senior Data Engineer - Data &amp; ML Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,157 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sr. Development Support Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Radiology Partners</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Genworth</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Testing Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Select Minds LLC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; ML Platform</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,24 +2656,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2691,24 +2691,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,122 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,122 +801,122 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2621,24 +2621,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
@@ -2877,111 +2877,6 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,104 +766,104 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,24 +2621,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,190 +2691,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Data &amp; ML Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,42 +2176,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,87 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; ML Platform</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,94 +1721,94 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,147 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,60 +478,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8061f8dcfa3609</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
+          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,69 +1641,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,24 +1921,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2202a6927a5be308</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=4cce85be0ed0449c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,15 +2481,190 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Java)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr. Development Support Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Radiology Partners</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Genworth</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Testing Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Select Minds LLC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,120 +478,120 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8061f8dcfa3609</t>
+          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>10X Genomics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,234 +601,234 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10X Genomics</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,50 +1283,50 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Test Engineer (JUnit, TestNG)</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,24 +1921,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2202a6927a5be308</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,139 +1991,139 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cce85be0ed0449c</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,260 +2411,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,69 +1956,69 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,122 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,67 +1913,67 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,24 +2166,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,120 +2201,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,50 +1843,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,85 +2131,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer III</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef9390b5f4c6d99</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb90377e9afbaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10X Genomics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>SOC Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Kafka, Kafka Connect, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ec1afd188dfb2</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer (II or Senior) - Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Distro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4da24314e707fe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Sr. Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbf2d9f2840f1dd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a7142d0678ce23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Identity Security Fundamentals Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec444e19fb1a980</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Full Stack Trainee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,77 +1536,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0f98184675c10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Anika Systems</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer-5</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb5a89eeb259f5e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,94 +1816,94 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=c88986bdf4181f36</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=319a55305b9ec532</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>AI/ML Strategy Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, Hive, Sqoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=ab46dd91496e3ce4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1952,98 +1952,98 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Java)</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,287 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Java SDK / Library Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Java)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Java)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Java)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Java)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Database Administrator</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FINBOA INC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, ETL, CI/CD, Azure DevOps, Git, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a06d010c371b71c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CrowdStrike Security Trainee</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a27bacbcbe153698</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-25.xlsx
+++ b/results/job_matches_2026-04-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,147 +478,147 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
+          <t>https://www.indeed.com/viewjob?jk=1dc7f9cc9fc3230a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ef9390b5f4c6d99</t>
+          <t>https://www.indeed.com/viewjob?jk=7b29c302cd453d25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rocky Mountain Elk Foundation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Missoula, MT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b68f7381cd9ed0c</t>
+          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rocky Mountain Elk Foundation</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Missoula, MT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,139 +626,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9015f8bca6247309</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, Spark, PySpark, Scala, Kafka, Dask</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f385096f84df36</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOC Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nimble</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Kafka, Kafka Connect, Splunk, CI/CD, Jenkins</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ec1afd188dfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Platform Engineer [Data Bricks]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dec88435b36ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Fulfillment Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nimble</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=468bb000278c0677</t>
+          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer- Fulfillment Team</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73dbee285af86aa</t>
+          <t>https://www.indeed.com/viewjob?jk=58e46008e082a2c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer [Data Bricks]</t>
+          <t>Data Engineer - Guidewire</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18261c9b6c504054</t>
+          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer (II or Senior) - Backend</t>
+          <t>Senior Azure Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Distro</t>
+          <t>CENTSTONE SERVICES LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hazlet, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4da24314e707fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Fulfillment Team</t>
+          <t>Database Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dbf2d9f2840f1dd</t>
+          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Azure Data Architect</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CENTSTONE SERVICES LLC</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hazlet, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe25b3fd6142a55</t>
+          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Engineer I</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Webster, NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08825b384c423d58</t>
+          <t>https://www.indeed.com/viewjob?jk=6325226098b53d8c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Guidewire</t>
+          <t>Senior AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Naphcare, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f88d6fa0c8b08ab</t>
+          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013d953c5d331236</t>
+          <t>https://www.indeed.com/viewjob?jk=aca797da11c35d09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Platform Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Naphcare, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, SQL Server</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e1c69114e7cd26</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe726b1c2405926</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Software Engineer, Testing</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b563dee50b08e5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d88c948e0a02d22</t>
+          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Testing</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7802ea905344bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>RailPros</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf27ac27278cdd4a</t>
+          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6ae794e568483d</t>
+          <t>https://www.indeed.com/viewjob?jk=8debac1e37803644</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RailPros</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877de91c46c5222a</t>
+          <t>https://www.indeed.com/viewjob?jk=2514363f9f331d84</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f510815207394b27</t>
+          <t>https://www.indeed.com/viewjob?jk=d1fe80d6798d0d76</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Java Solution Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
+          <t>https://www.indeed.com/viewjob?jk=55187d9137ae191d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
+          <t>https://www.indeed.com/viewjob?jk=a9867f7f794e3fe9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,24 +1431,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a7142d0678ce23</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d70e0445efdf5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Identity Security Fundamentals Analyst</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec444e19fb1a980</t>
+          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,174 +1501,174 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Azure, Databricks, Scala, SQL Server, ETL, ELT, pytest, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a0c460d70b3958</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bcf9a250ecec1a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Trainee</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0f98184675c10</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate - Data Engineering</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, Kafka, Snowflake, ETL, ELT, dbt, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1dc3272f5f9117</t>
+          <t>https://www.indeed.com/viewjob?jk=7c8deb9cfaee37ff</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anika Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Spark, Time Travel, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Google Cloud Platform, Vertex AI, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96965ccd7aa4c5af</t>
+          <t>https://www.indeed.com/viewjob?jk=90f877954706efc9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3fe7c74b8687e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7601454f8dffc4f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2bed86f78e502e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
+          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb5a89eeb259f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1e880d8a206058</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Full Stack Developer - AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Greater NY Insurance Companies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,59 +1816,59 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, Oracle, NoSQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88986bdf4181f36</t>
+          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Engineering</t>
+          <t>API Architect (Python)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319a55305b9ec532</t>
+          <t>https://www.indeed.com/viewjob?jk=6cf022575a6c3cfb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI/ML Strategy Consultant</t>
+          <t>Security Backend Engineer (Python)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Hive, Sqoop, Spark, PySpark, Oracle, SQL Server, ETL</t>
+          <t>Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab46dd91496e3ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5cd842269d8636</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a4416ae7220f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Java SDK / Library Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,84 +1966,84 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1cde807edc03031</t>
+          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer - AI</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Greater NY Insurance Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, ETL, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307da76aaf0a9803</t>
+          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcc4b728c62daf1</t>
+          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312ff9af965f2503</t>
+          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
+          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Full Stack Developer (Java)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00375f8fa1a5cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9f35cb639fca25e4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java SDK / Library Developer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,227 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, Git</t>
+          <t>AWS, ECS, RDS, Scala, ETL, dbt, Tableau, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af205ded49a4f91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=147278d42a645e19</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b145de3d65c1aa82</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=022a0b1399684a50</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Full Stack Developer (Java)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, MicroStrategy, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bea96c3fb8d5453</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Database Administrator</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FINBOA INC</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, ETL, CI/CD, Azure DevOps, Git, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a06d010c371b71c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CrowdStrike Security Trainee</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a27bacbcbe153698</t>
+          <t>https://www.indeed.com/viewjob?jk=3066b4b418c04c55</t>
         </is>
       </c>
     </row>
